--- a/data/Dolar-2.xlsx
+++ b/data/Dolar-2.xlsx
@@ -383,9 +383,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>280440</xdr:colOff>
+      <xdr:colOff>280080</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>73440</xdr:rowOff>
+      <xdr:rowOff>73080</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -397,7 +397,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="6621840"/>
-          <a:ext cx="280440" cy="273960"/>
+          <a:ext cx="280080" cy="273600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4312,17 +4312,17 @@
     </row>
     <row r="116" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="16" t="n">
-        <v>46185</v>
+        <v>46203</v>
       </c>
       <c r="B116" s="10" t="n">
-        <v>1430</v>
+        <v>1495</v>
       </c>
       <c r="C116" s="10" t="n">
-        <v>1450</v>
+        <v>1515</v>
       </c>
       <c r="D116" s="10" t="n">
         <f aca="false">+(B116+C116)/2</f>
-        <v>1440</v>
+        <v>1505</v>
       </c>
       <c r="E116" s="11" t="n">
         <f aca="false">+C116-B116</f>
@@ -4330,19 +4330,19 @@
       </c>
       <c r="F116" s="7" t="n">
         <f aca="false">+LN(B116/B115)*100</f>
-        <v>1.4084739881739</v>
+        <v>5.85365024525729</v>
       </c>
       <c r="G116" s="7" t="n">
         <f aca="false">+LN(C116/C115)*100</f>
-        <v>1.38891121606671</v>
+        <v>5.77409946895165</v>
       </c>
       <c r="H116" s="8" t="n">
         <f aca="false">+F116</f>
-        <v>1.4084739881739</v>
+        <v>5.85365024525729</v>
       </c>
       <c r="I116" s="8" t="n">
         <f aca="false">+G116</f>
-        <v>1.38891121606671</v>
+        <v>5.77409946895165</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
